--- a/worklog/v2.2.1/req/pm/project1.xlsx
+++ b/worklog/v2.2.1/req/pm/project1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10695"/>
+    <workbookView windowWidth="28800" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>项目编号</t>
   </si>
@@ -44,6 +44,9 @@
     <t>节点计划周数</t>
   </si>
   <si>
+    <t>交付物</t>
+  </si>
+  <si>
     <t>节点类型</t>
   </si>
   <si>
@@ -108,6 +111,9 @@
   </si>
   <si>
     <t>最后更新时间</t>
+  </si>
+  <si>
+    <t>最后更新月数</t>
   </si>
   <si>
     <t>填写人</t>
@@ -126,14 +132,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,133 +605,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -740,7 +739,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1268,10 +1267,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr defaultColWidth="8.96666666666667" defaultRowHeight="17.6"/>
   <sheetData>
-    <row r="1" ht="52.9" spans="1:29">
+    <row r="1" ht="52.9" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1358,6 +1357,12 @@
       </c>
       <c r="AC1" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
